--- a/data/Input_TKB_V8.xlsx
+++ b/data/Input_TKB_V8.xlsx
@@ -191,12 +191,7 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Số tiết tối đa mỗi tuần (người hưởng thai sản ghi mức đã giảm).</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Ghi "Có" nếu đang hưởng chế độ thai sản; để trống nếu không.</t>
+        <t>Số tiết tối đa mỗi tuần.</t>
       </text>
     </comment>
   </commentList>
@@ -492,14 +487,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E300"/>
+  <dimension ref="A1:D300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -523,11 +517,6 @@
           <t>Số Tiết/Tuần</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Chế Độ</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -548,7 +537,6 @@
       <c r="D2" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E2" s="3" t="n"/>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -569,7 +557,6 @@
       <c r="D3" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E3" s="3" t="n"/>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -590,7 +577,6 @@
       <c r="D4" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E4" s="3" t="n"/>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -611,7 +597,6 @@
       <c r="D5" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E5" s="3" t="n"/>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -632,7 +617,6 @@
       <c r="D6" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E6" s="3" t="n"/>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -653,7 +637,6 @@
       <c r="D7" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E7" s="3" t="n"/>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -674,7 +657,6 @@
       <c r="D8" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E8" s="3" t="n"/>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -695,7 +677,6 @@
       <c r="D9" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E9" s="3" t="n"/>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -716,7 +697,6 @@
       <c r="D10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E10" s="3" t="n"/>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -737,7 +717,6 @@
       <c r="D11" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E11" s="3" t="n"/>
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -758,7 +737,6 @@
       <c r="D12" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E12" s="3" t="n"/>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -779,7 +757,6 @@
       <c r="D13" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E13" s="3" t="n"/>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -800,7 +777,6 @@
       <c r="D14" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E14" s="3" t="n"/>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -821,7 +797,6 @@
       <c r="D15" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E15" s="3" t="n"/>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -842,7 +817,6 @@
       <c r="D16" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E16" s="3" t="n"/>
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -863,7 +837,6 @@
       <c r="D17" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E17" s="3" t="n"/>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -884,7 +857,6 @@
       <c r="D18" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E18" s="3" t="n"/>
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -905,7 +877,6 @@
       <c r="D19" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E19" s="3" t="n"/>
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -926,7 +897,6 @@
       <c r="D20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E20" s="3" t="n"/>
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -947,7 +917,6 @@
       <c r="D21" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E21" s="3" t="n"/>
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -968,7 +937,6 @@
       <c r="D22" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E22" s="3" t="n"/>
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -989,7 +957,6 @@
       <c r="D23" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E23" s="3" t="n"/>
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -1010,7 +977,6 @@
       <c r="D24" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E24" s="3" t="n"/>
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -1031,7 +997,6 @@
       <c r="D25" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E25" s="3" t="n"/>
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1052,7 +1017,6 @@
       <c r="D26" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E26" s="3" t="n"/>
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -1073,7 +1037,6 @@
       <c r="D27" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E27" s="3" t="n"/>
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -1094,7 +1057,6 @@
       <c r="D28" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E28" s="3" t="n"/>
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -1115,12 +1077,11 @@
       <c r="D29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E29" s="3" t="n"/>
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên CN 29 (Thai sản)</t>
+          <t>Giáo viên CN 29</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1135,11 +1096,6 @@
       </c>
       <c r="D30" s="3" t="n">
         <v>16</v>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
@@ -1157,7 +1113,6 @@
       <c r="D31" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E31" s="3" t="n"/>
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -1174,7 +1129,6 @@
       <c r="D32" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E32" s="3" t="n"/>
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -1191,7 +1145,6 @@
       <c r="D33" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E33" s="3" t="n"/>
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -1208,12 +1161,11 @@
       <c r="D34" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E34" s="3" t="n"/>
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên BM 5 (Thai sản)</t>
+          <t>Giáo viên BM 5</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1224,11 +1176,6 @@
       <c r="C35" s="4" t="n"/>
       <c r="D35" s="3" t="n">
         <v>19</v>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1">
@@ -1246,7 +1193,6 @@
       <c r="D36" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E36" s="3" t="n"/>
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -1263,7 +1209,6 @@
       <c r="D37" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E37" s="3" t="n"/>
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -1280,7 +1225,6 @@
       <c r="D38" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E38" s="3" t="n"/>
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -1297,7 +1241,6 @@
       <c r="D39" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E39" s="3" t="n"/>
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -1314,7 +1257,6 @@
       <c r="D40" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E40" s="3" t="n"/>
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -1331,7 +1273,6 @@
       <c r="D41" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E41" s="3" t="n"/>
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -1348,7 +1289,6 @@
       <c r="D42" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E42" s="3" t="n"/>
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -1365,7 +1305,6 @@
       <c r="D43" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E43" s="3" t="n"/>
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -1382,7 +1321,6 @@
       <c r="D44" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E44" s="3" t="n"/>
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -1399,7 +1337,6 @@
       <c r="D45" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E45" s="3" t="n"/>
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -1416,77 +1353,66 @@
       <c r="D46" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E46" s="3" t="n"/>
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="2" t="n"/>
       <c r="B47" s="3" t="n"/>
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n"/>
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="2" t="n"/>
       <c r="B48" s="3" t="n"/>
       <c r="C48" s="4" t="n"/>
       <c r="D48" s="3" t="n"/>
-      <c r="E48" s="3" t="n"/>
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="2" t="n"/>
       <c r="B49" s="3" t="n"/>
       <c r="C49" s="4" t="n"/>
       <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n"/>
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="2" t="n"/>
       <c r="B50" s="3" t="n"/>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="3" t="n"/>
-      <c r="E50" s="3" t="n"/>
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="2" t="n"/>
       <c r="B51" s="3" t="n"/>
       <c r="C51" s="4" t="n"/>
       <c r="D51" s="3" t="n"/>
-      <c r="E51" s="3" t="n"/>
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="2" t="n"/>
       <c r="B52" s="3" t="n"/>
       <c r="C52" s="4" t="n"/>
       <c r="D52" s="3" t="n"/>
-      <c r="E52" s="3" t="n"/>
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="2" t="n"/>
       <c r="B53" s="3" t="n"/>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n"/>
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="2" t="n"/>
       <c r="B54" s="3" t="n"/>
       <c r="C54" s="4" t="n"/>
       <c r="D54" s="3" t="n"/>
-      <c r="E54" s="3" t="n"/>
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="2" t="n"/>
       <c r="B55" s="3" t="n"/>
       <c r="C55" s="4" t="n"/>
       <c r="D55" s="3" t="n"/>
-      <c r="E55" s="3" t="n"/>
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="2" t="n"/>
       <c r="B56" s="3" t="n"/>
       <c r="C56" s="4" t="n"/>
       <c r="D56" s="3" t="n"/>
-      <c r="E56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="C57" s="5" t="n"/>
@@ -2230,7 +2156,7 @@
       <formula>AND($C2&lt;&gt;"",$B2&lt;&gt;"Chủ Nhiệm")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation sqref="B2:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Danh mục'!$A$1:$A$8</formula1>
     </dataValidation>
@@ -2240,9 +2166,6 @@
     <dataValidation sqref="D2:D300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Số tiết không hợp lệ" error="Số tiết là số nguyên từ 0 đến 40." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>40</formula2>
-    </dataValidation>
-    <dataValidation sqref="E2:E300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Chế Độ" error="Ghi &quot;Có&quot; hoặc để trống." type="list">
-      <formula1>"Có"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
